--- a/runac/demo/DISP_PENAL_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
+++ b/runac/demo/DISP_PENAL_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
@@ -12,10 +12,9 @@
     <sheet name="MPT" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="CAD" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Guardia Comisaría" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="categ prision domi" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="INSTRUCCIONES" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="LISTAS" sheetId="8" state="hidden" r:id="rId8"/>
-    <sheet name="ADVERTENCIAS_ESPERADAS" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="INSTRUCCIONES" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="LISTAS" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet name="ADVERTENCIAS_ESPERADAS" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1222,40 +1221,6 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>RUNAC</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>Nombre del dispositvo
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>Dependencia institucional
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>El equipo de niñez provincial realiza seguimiento de los adolescentes bajo esta modalidad
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -24933,554 +24898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="48" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Nombre del dispositvo *</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Dependencia institucional</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>El equipo de niñez provincial realiza seguimiento de los adolescentes bajo esta modalidad</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Centro Municipal Norte</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Ministerio de Desarrollo Social</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Centro Municipal Norte</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Servicio de Protección de Derechos</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Hogar Los Álamos</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Subsecretaría de Niñez y Adolescencia</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Hogar Los Álamos</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Municipalidad de Rawson</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Hogar Los Álamos</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Ministerio de Desarrollo Social</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Hogar Nuestra Señora</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Ministerio de Desarrollo Social</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Residencia El Ceibo</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Servicio de Protección de Derechos</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Residencia El Ceibo</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Servicio de Protección de Derechos</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Residencia El Ceibo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Subsecretaría de Niñez y Adolescencia</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Programa de Acompañamiento Sur</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Convenio con organización civil</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Hogar Los Álamos</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Servicio de Protección de Derechos</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Hogar Los Álamos</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Municipalidad de Rawson</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Residencia El Ceibo</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Servicio de Protección de Derechos</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Residencia El Ceibo</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Convenio con organización civil</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Hogar Los Álamos</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Ministerio de Desarrollo Social</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Centro Municipal Norte</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Convenio con organización civil</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Centro Municipal Norte</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Servicio de Protección de Derechos</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Centro Municipal Norte</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Municipalidad de Rawson</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Programa de Acompañamiento Sur</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Subsecretaría de Niñez y Adolescencia</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Programa de Acompañamiento Sur</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Subsecretaría de Niñez y Adolescencia</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Residencia El Ceibo</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Municipalidad de Rawson</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Centro Municipal Norte</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Servicio de Protección de Derechos</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Hogar Nuestra Señora</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Convenio con organización civil</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Programa de Acompañamiento Sur</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Convenio con organización civil</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Hogar Los Álamos</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Secretaría de Niñez, Adolescencia y Familia</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Hogar Nuestra Señora</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Servicio de Protección de Derechos</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Centro Municipal Norte</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Convenio con organización civil</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Hogar Nuestra Señora</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Convenio con organización civil</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Centro Municipal Norte</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Subsecretaría de Niñez y Adolescencia</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Hogar Los Álamos</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Municipalidad de Rawson</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B133"/>
+  <dimension ref="A1:B128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -26738,47 +26156,12 @@
       </c>
       <c r="B128" s="7" t="n"/>
     </row>
-    <row r="130">
-      <c r="A130" s="6" t="inlineStr">
-        <is>
-          <t>Hoja: categ prision domi</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Nombre del dispositvo</t>
-        </is>
-      </c>
-      <c r="B131" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Dependencia institucional</t>
-        </is>
-      </c>
-      <c r="B132" s="7" t="n"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>El equipo de niñez provincial realiza seguimiento de los adolescentes bajo esta modalidad</t>
-        </is>
-      </c>
-      <c r="B133" s="7" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26936,7 +26319,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
